--- a/quizzes/035_proportional_detector_understanding_quiz--quizzes.xlsx
+++ b/quizzes/035_proportional_detector_understanding_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>questions_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>What is a Proportional Detector?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,58 +543,58 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>confidence_rating_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>What is the main purpose of a Proportional Detector?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>How does a Proportional Detector detect its surroundings?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>questions_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>What kind of data does a Proportional Detector usually detect?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,35 +612,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>confidence_rating_2</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>How does one calibrate a Proportional Detector?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>submit_button_1</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>What are the common applications of a Proportional Detector?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>questions_3</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Can a Proportional Detector be used in multiple frequencies?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,110 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>confidence_rating_3</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>How accurate is a Proportional Detector in its readings?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>question_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What are the limitations of a Proportional Detector?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>question_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Can a Proportional Detector be used in real-time environments?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>question_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the typical workflow when setting up a Proportional Detector?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>question_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What kind of error checking is performed by a Proportional Detector?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,68 +827,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submit_button_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>geometric_data</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Geometric data</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>submit_button_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>magnetic_data</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Magnetic data</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>submit_button_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>electromagnetic_data</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Electromagnetic data</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>submit_button_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>geophysics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Geophysics</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>biophysics</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Biophysics</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>electrotechnics</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Electrotechnics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
